--- a/DataTable/Datas/__tables__.xlsx
+++ b/DataTable/Datas/__tables__.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19830" windowHeight="8265"/>
+    <workbookView windowWidth="28800" windowHeight="11240"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
   <si>
     <t>##var</t>
   </si>
@@ -110,31 +110,13 @@
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
   </si>
   <si>
-    <t>Game.TbSkillConfig</t>
-  </si>
-  <si>
-    <t>SkillConfig</t>
-  </si>
-  <si>
-    <t>主玩法/S. Skill.xlsx</t>
-  </si>
-  <si>
-    <t>Game.TbBuffConfig</t>
-  </si>
-  <si>
-    <t>BuffConfig</t>
-  </si>
-  <si>
-    <t>主玩法/B. Buff.xlsx</t>
-  </si>
-  <si>
-    <t>Game.TbActionConfig</t>
-  </si>
-  <si>
-    <t>ActionConfig</t>
-  </si>
-  <si>
-    <t>主玩法/A. Action.xlsx</t>
+    <t>Demo.TbDemoConfig</t>
+  </si>
+  <si>
+    <t>DemoConfig</t>
+  </si>
+  <si>
+    <t>DemoConfig.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1076,13 +1058,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="3"/>
   <cols>
-    <col min="2" max="2" width="20.3833333333333" customWidth="1"/>
-    <col min="3" max="3" width="15.575" customWidth="1"/>
-    <col min="4" max="4" width="32.425" customWidth="1"/>
-    <col min="5" max="5" width="24.3833333333333" customWidth="1"/>
+    <col min="2" max="2" width="20.3839285714286" customWidth="1"/>
+    <col min="3" max="3" width="15.5714285714286" customWidth="1"/>
+    <col min="4" max="4" width="32.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="24.3839285714286" customWidth="1"/>
     <col min="6" max="9" width="18" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1188,34 +1170,6 @@
       </c>
       <c r="E4" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5">
-      <c r="B5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5">
-      <c r="B6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
